--- a/_readme/programs-info.xlsx
+++ b/_readme/programs-info.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t xml:space="preserve">Filename</t>
   </si>
@@ -28,70 +28,118 @@
     <t xml:space="preserve">Note</t>
   </si>
   <si>
-    <t xml:space="preserve">./global-libraries.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defines libraries used globally in various pieces (text, analysis, and documentation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./pathconfig.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defines various relative paths</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./programs/01_download_replication_data.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Download the Replication Lab data from Zenodo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./programs/02_get_crossref.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Old program to get Crossref info on articles. May no longer work. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">./programs/10_analysis.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./programs/20_appendix.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appendix analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./programs/30_intext.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prints out any in-text numbers not otherwise computed in tables.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./programs/99_zz_info.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System information</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./programs/config.R</t>
+    <t xml:space="preserve">config.R</t>
   </si>
   <si>
     <t xml:space="preserve">Basic configuration</t>
   </si>
   <si>
-    <t xml:space="preserve">./programs/libraries.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All libraries used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./text/libraries.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional libraries (possibly no longer relevant, kept for robustness)</t>
+    <t xml:space="preserve">code/libraries.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines libraries used globally in various pieces (data acquisition, analysis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/01_compute_econphd.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computes the number of Econ grads from NSF data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/02_convert_tables.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Converts variables tables from Excel to LaTeX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/03_tabulate_access_aea.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reads private AEA data and writes cleaned data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/04_tabulate_access_categories.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabulate AEA access outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/11_get_crossref.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get full list of NBER publications, print out in-text numbers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/13_analyse_authors.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unduplicates authors, prints out in-text numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/20_geocode_stata_step1.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses data provided by Kit Baum and writes out intermediate file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/21_geocode_stata_step2.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses Geolite database and host command to identify geography of IP addresses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/22_generate_download_map.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses geocoded download data to create map.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/25_download_R_logs.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download Posit/CRAN logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/26_aggregate_data.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggregates Posit/CRAN data by country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/27_map_R_by_country.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creates maps, and computes regional statistics for R download</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/28_stata_map_by_country.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creates maps, and computes regional statistics for Stata download</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/29_compare_stata_r_by_region.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loads the regional and North/South statistics from the R and Stata analyses, # computes the percent difference, and outputs combined tables and a horizontal histogram of differences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/99_zz_info.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System information on the system running the code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/99_zzz_compile_readme.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiles the README</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_readme/libraries.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines libraries used for the documentation only</t>
   </si>
 </sst>
 </file>
@@ -298,8 +346,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.62"/>
   </cols>
@@ -332,7 +380,7 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="0" t="s">
         <v>7</v>
       </c>
     </row>
@@ -340,7 +388,7 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>9</v>
       </c>
     </row>
@@ -348,7 +396,7 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>11</v>
       </c>
     </row>
@@ -356,7 +404,7 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>13</v>
       </c>
     </row>
@@ -364,7 +412,7 @@
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>15</v>
       </c>
     </row>
@@ -372,7 +420,7 @@
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="0" t="s">
         <v>17</v>
       </c>
     </row>
@@ -380,7 +428,7 @@
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>19</v>
       </c>
     </row>
@@ -388,7 +436,7 @@
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="0" t="s">
         <v>21</v>
       </c>
     </row>
@@ -396,9 +444,109 @@
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/_readme/programs-info.xlsx
+++ b/_readme/programs-info.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t xml:space="preserve">Filename</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t xml:space="preserve">Tabulate AEA access outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code/05_software-usage-only-2019.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-print figure from Vilhuber (2020a) with better layout on software usage over time</t>
   </si>
   <si>
     <t xml:space="preserve">code/11_get_crossref.R</t>
@@ -346,7 +352,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.62"/>
@@ -380,7 +386,7 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -388,7 +394,7 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -396,7 +402,7 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -404,7 +410,7 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -412,7 +418,7 @@
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -420,7 +426,7 @@
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -428,7 +434,7 @@
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -436,7 +442,7 @@
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -444,7 +450,7 @@
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -452,7 +458,7 @@
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -460,7 +466,7 @@
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -468,7 +474,7 @@
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -476,7 +482,7 @@
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -484,7 +490,7 @@
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -492,7 +498,7 @@
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -500,7 +506,7 @@
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -508,46 +514,30 @@
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0"/>
-    </row>
+      <c r="A21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
